--- a/input_data/input_data_common_start.xlsx
+++ b/input_data/input_data_common_start.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87C639A-A73D-4D96-B1E0-129ECCA86FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA49811-00BD-47D8-9361-E7F090AA446C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="796" activeTab="1" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="4" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="18" r:id="rId1"/>
@@ -27,20 +27,21 @@
     <sheet name="cf" sheetId="7" r:id="rId12"/>
     <sheet name="inflow" sheetId="3" r:id="rId13"/>
     <sheet name="inflow_blocks" sheetId="22" r:id="rId14"/>
-    <sheet name="price" sheetId="4" r:id="rId15"/>
-    <sheet name="markets" sheetId="5" r:id="rId16"/>
-    <sheet name="reserve_realisation" sheetId="23" r:id="rId17"/>
-    <sheet name="bid_slots" sheetId="28" r:id="rId18"/>
-    <sheet name="market_prices" sheetId="8" r:id="rId19"/>
-    <sheet name="balance_prices" sheetId="20" r:id="rId20"/>
-    <sheet name="reserve_activation_price" sheetId="27" r:id="rId21"/>
-    <sheet name="risk" sheetId="17" r:id="rId22"/>
-    <sheet name="scenarios" sheetId="9" r:id="rId23"/>
-    <sheet name="fixed_ts" sheetId="11" r:id="rId24"/>
-    <sheet name="eff_ts" sheetId="12" r:id="rId25"/>
-    <sheet name="constraints" sheetId="14" r:id="rId26"/>
-    <sheet name="gen_constraint" sheetId="15" r:id="rId27"/>
-    <sheet name="cap_ts" sheetId="16" r:id="rId28"/>
+    <sheet name="flex_inflow" sheetId="29" r:id="rId15"/>
+    <sheet name="price" sheetId="4" r:id="rId16"/>
+    <sheet name="markets" sheetId="5" r:id="rId17"/>
+    <sheet name="reserve_realisation" sheetId="23" r:id="rId18"/>
+    <sheet name="bid_slots" sheetId="28" r:id="rId19"/>
+    <sheet name="market_prices" sheetId="8" r:id="rId20"/>
+    <sheet name="balance_prices" sheetId="20" r:id="rId21"/>
+    <sheet name="reserve_activation_price" sheetId="27" r:id="rId22"/>
+    <sheet name="risk" sheetId="17" r:id="rId23"/>
+    <sheet name="scenarios" sheetId="9" r:id="rId24"/>
+    <sheet name="fixed_ts" sheetId="11" r:id="rId25"/>
+    <sheet name="eff_ts" sheetId="12" r:id="rId26"/>
+    <sheet name="constraints" sheetId="14" r:id="rId27"/>
+    <sheet name="gen_constraint" sheetId="15" r:id="rId28"/>
+    <sheet name="cap_ts" sheetId="16" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="168">
   <si>
     <t>node</t>
   </si>
@@ -549,6 +550,21 @@
   </si>
   <si>
     <t>common_end_timesteps</t>
+  </si>
+  <si>
+    <t>period_name</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>t_start</t>
+  </si>
+  <si>
+    <t>t_end</t>
+  </si>
+  <si>
+    <t>inflow</t>
   </si>
 </sst>
 </file>
@@ -601,13 +617,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -630,9 +643,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -670,7 +683,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -776,7 +789,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -918,7 +931,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -927,169 +940,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39053E69-3A75-490E-847C-66A9CF6C1FC5}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="4"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="4"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="4"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="4"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="4"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="4"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="4"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="4"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="4"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="4"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="4"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1099,158 +1112,158 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA355BEF-1F4B-494A-B089-4FCDFFFA57F7}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -1264,17 +1277,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0532F8A-0FB4-47AD-98A1-4065D3376432}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -1282,7 +1295,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -1298,33 +1311,33 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4637A-7829-48D6-AE54-2E654AB1A427}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="23.140625" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="23.109375" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>82</v>
       </c>
       <c r="F1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -1342,11 +1355,11 @@
         <f>1*C2</f>
         <v>0.2</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="L2" s="7"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="F2" s="4"/>
+      <c r="L2" s="4"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -1365,8 +1378,8 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -1385,8 +1398,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -1405,8 +1418,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -1425,116 +1438,116 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -1549,38 +1562,38 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F87DD44-A1AD-4241-AED7-C48CC9DEE2E2}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
-    <col min="4" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
+    <col min="4" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -1598,17 +1611,17 @@
         <f>1*C2</f>
         <v>-5</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2">
         <f>1*B2</f>
         <v>-5</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2">
         <f>1*C2</f>
         <v>-5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -1626,17 +1639,17 @@
         <f t="shared" ref="E3:E6" si="0">1*C3</f>
         <v>-5</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3">
         <f t="shared" ref="F3:F6" si="1">1*B3</f>
         <v>-5</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3">
         <f t="shared" ref="G3:G6" si="2">1*C3</f>
         <v>-5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -1654,17 +1667,17 @@
         <f t="shared" si="0"/>
         <v>-6</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4">
         <f t="shared" si="1"/>
         <v>-4</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4">
         <f t="shared" si="2"/>
         <v>-6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -1682,17 +1695,17 @@
         <f t="shared" si="0"/>
         <v>-3</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5">
         <f t="shared" si="1"/>
         <v>-2</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5">
         <f t="shared" si="2"/>
         <v>-3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -1710,166 +1723,147 @@
         <f t="shared" si="0"/>
         <v>-4</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6">
         <f t="shared" si="1"/>
         <v>-7</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6">
         <f t="shared" si="2"/>
         <v>-4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
+      <c r="G7"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
+      <c r="G8"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
+      <c r="G9"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
+      <c r="G10"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
+      <c r="G11"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
+      <c r="G12"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
+      <c r="G13"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
+      <c r="G14"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
+      <c r="G15"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
+      <c r="G16"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
+      <c r="G17"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
+      <c r="G18"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
+      <c r="G19"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
+      <c r="G20"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
+      <c r="G21"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
+      <c r="G22"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
+      <c r="G23"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
+      <c r="G24"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="G25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1881,15 +1875,15 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098BD40C-3F1E-4DCA-B153-EDE213641CC0}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -1918,96 +1912,96 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="4">
         <v>44671.041666666664</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>-2</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <v>-2</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2">
         <v>-2</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="4">
         <v>44671.124999826388</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2">
         <v>-1</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2">
         <v>-2</v>
       </c>
-      <c r="I2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="4">
         <v>44671.08333321759</v>
       </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4">
         <v>44671.166666435187</v>
       </c>
-      <c r="G3" s="2">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3">
         <v>-1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="4">
         <v>44671.124999826388</v>
       </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C5" s="7"/>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2015,371 +2009,212 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17ADD341-DF79-42C4-A9D4-008C7FE8FB1E}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44671</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44671.041666666664</v>
-      </c>
-      <c r="B3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44671.08333321759</v>
-      </c>
-      <c r="B4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44671.124999826388</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44671.166666435187</v>
-      </c>
-      <c r="B6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44671</v>
+      </c>
+      <c r="B2">
         <v>12</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0</v>
-      </c>
-      <c r="K2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J3" s="6">
-        <v>10</v>
-      </c>
-      <c r="K3" s="6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6">
-        <v>0</v>
-      </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J5" s="6">
-        <v>5</v>
-      </c>
-      <c r="K5" s="6">
-        <v>50</v>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44671.041666666664</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44671.08333321759</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44671.124999826388</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44671.166666435187</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2388,16 +2223,209 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="3">
+        <v>10</v>
+      </c>
+      <c r="K3" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J5" s="3">
+        <v>5</v>
+      </c>
+      <c r="K5" s="3">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21372C5-DB60-4318-868D-D4FA20FECD5D}">
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
-    <col min="2" max="3" width="6.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
+    <col min="2" max="3" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B1" t="s">
@@ -2428,8 +2456,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -2461,8 +2489,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -2494,8 +2522,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -2527,8 +2555,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -2560,8 +2588,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -2593,119 +2621,119 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -2716,569 +2744,164 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B77AB47-4DF2-4CE7-989A-6ED48E9B6093}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
-    <col min="2" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="13" width="11.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44671</v>
-      </c>
-      <c r="B2">
-        <v>48</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <f>B2</f>
-        <v>48</v>
-      </c>
-      <c r="G2">
-        <f t="shared" ref="G2:M2" si="0">C2</f>
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="J2">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="K2">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44671.041666666664</v>
-      </c>
-      <c r="B3">
-        <v>60</v>
-      </c>
-      <c r="C3">
-        <v>34</v>
-      </c>
-      <c r="D3">
-        <v>56</v>
-      </c>
-      <c r="E3">
-        <v>71</v>
-      </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F4" si="1">B3</f>
-        <v>60</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G4" si="2">C3</f>
-        <v>34</v>
-      </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H4" si="3">D3</f>
-        <v>56</v>
-      </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I4" si="4">E3</f>
-        <v>71</v>
-      </c>
-      <c r="J3">
-        <f t="shared" ref="J3:J4" si="5">F3</f>
-        <v>60</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K4" si="6">G3</f>
-        <v>34</v>
-      </c>
-      <c r="L3">
-        <f t="shared" ref="L3:L4" si="7">H3</f>
-        <v>56</v>
-      </c>
-      <c r="M3">
-        <f t="shared" ref="M3:M4" si="8">I3</f>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44671.08333321759</v>
-      </c>
-      <c r="B4">
-        <v>58</v>
-      </c>
-      <c r="C4">
-        <v>92</v>
-      </c>
-      <c r="D4">
-        <v>44</v>
-      </c>
-      <c r="E4">
-        <v>42</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="2"/>
-        <v>92</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="J4">
-        <f t="shared" si="5"/>
-        <v>58</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="6"/>
-        <v>92</v>
-      </c>
-      <c r="L4">
-        <f t="shared" si="7"/>
-        <v>44</v>
-      </c>
-      <c r="M4">
-        <f t="shared" si="8"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44671.124999826388</v>
-      </c>
-      <c r="B5">
-        <v>51</v>
-      </c>
-      <c r="C5">
-        <v>66</v>
-      </c>
-      <c r="D5">
-        <v>86</v>
-      </c>
-      <c r="E5">
-        <v>39</v>
-      </c>
-      <c r="F5">
-        <v>76.5</v>
-      </c>
-      <c r="G5">
-        <v>79.2</v>
-      </c>
-      <c r="H5">
-        <v>103.2</v>
-      </c>
-      <c r="I5">
-        <v>46.8</v>
-      </c>
-      <c r="J5">
-        <v>25.5</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44671.166666435187</v>
-      </c>
-      <c r="B6">
-        <v>37</v>
-      </c>
-      <c r="C6">
-        <v>64</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>78</v>
-      </c>
-      <c r="F6">
-        <v>55.5</v>
-      </c>
-      <c r="G6">
-        <v>76.8</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>93.6</v>
-      </c>
-      <c r="J6">
-        <v>18.5</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3286,21 +2909,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82624B08-6930-4D2B-BCBB-C78CE759E704}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>141</v>
       </c>
@@ -3308,7 +2931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>137</v>
       </c>
@@ -3316,7 +2939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>138</v>
       </c>
@@ -3324,7 +2947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>139</v>
       </c>
@@ -3332,7 +2955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>140</v>
       </c>
@@ -3340,7 +2963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>155</v>
       </c>
@@ -3348,7 +2971,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>156</v>
       </c>
@@ -3356,7 +2979,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>161</v>
       </c>
@@ -3364,7 +2987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>162</v>
       </c>
@@ -3372,7 +2995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>142</v>
       </c>
@@ -3387,298 +3010,400 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="7" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
+    <col min="2" max="5" width="11.44140625" customWidth="1"/>
+    <col min="6" max="13" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="B1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
       <c r="B2">
-        <f>1.1*market_prices!B2</f>
-        <v>52.800000000000004</v>
+        <v>48</v>
       </c>
       <c r="C2">
-        <f>1.1*market_prices!F2</f>
-        <v>52.800000000000004</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <f>1.1*market_prices!J2</f>
-        <v>52.800000000000004</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <f>0.9*market_prices!B2</f>
-        <v>43.2</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <f>0.9*market_prices!F2</f>
-        <v>43.2</v>
+        <f>B2</f>
+        <v>48</v>
       </c>
       <c r="G2">
-        <f>0.9*market_prices!J2</f>
-        <v>43.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+        <f t="shared" ref="G2:M2" si="0">C2</f>
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="J2">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
       <c r="B3">
-        <f>1.1*market_prices!B3</f>
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C3">
-        <f>1.1*market_prices!F3</f>
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <f>1.1*market_prices!J3</f>
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E3">
-        <f>0.9*market_prices!B3</f>
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F3">
-        <f>0.9*market_prices!F3</f>
-        <v>54</v>
+        <f t="shared" ref="F3:F4" si="1">B3</f>
+        <v>60</v>
       </c>
       <c r="G3">
-        <f>0.9*market_prices!J3</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+        <f t="shared" ref="G3:G4" si="2">C3</f>
+        <v>34</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H4" si="3">D3</f>
+        <v>56</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I4" si="4">E3</f>
+        <v>71</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J4" si="5">F3</f>
+        <v>60</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K4" si="6">G3</f>
+        <v>34</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L4" si="7">H3</f>
+        <v>56</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M4" si="8">I3</f>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
       <c r="B4">
-        <f>1.1*market_prices!B4</f>
-        <v>63.800000000000004</v>
+        <v>58</v>
       </c>
       <c r="C4">
-        <f>1.1*market_prices!F4</f>
-        <v>63.800000000000004</v>
+        <v>92</v>
       </c>
       <c r="D4">
-        <f>1.1*market_prices!J4</f>
-        <v>63.800000000000004</v>
+        <v>44</v>
       </c>
       <c r="E4">
-        <f>0.9*market_prices!B4</f>
-        <v>52.2</v>
+        <v>42</v>
       </c>
       <c r="F4">
-        <f>0.9*market_prices!F4</f>
-        <v>52.2</v>
+        <f t="shared" si="1"/>
+        <v>58</v>
       </c>
       <c r="G4">
-        <f>0.9*market_prices!J4</f>
-        <v>52.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+        <f t="shared" si="2"/>
+        <v>92</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="4"/>
+        <v>42</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="5"/>
+        <v>58</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="6"/>
+        <v>92</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="7"/>
+        <v>44</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="8"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
       <c r="B5">
-        <f>1.1*market_prices!B5</f>
-        <v>56.1</v>
+        <v>51</v>
       </c>
       <c r="C5">
-        <f>1.1*market_prices!F5</f>
-        <v>84.15</v>
+        <v>66</v>
       </c>
       <c r="D5">
-        <f>1.1*market_prices!J5</f>
-        <v>28.05</v>
+        <v>86</v>
       </c>
       <c r="E5">
-        <f>0.9*market_prices!B5</f>
-        <v>45.9</v>
+        <v>39</v>
       </c>
       <c r="F5">
-        <f>0.9*market_prices!F5</f>
-        <v>68.850000000000009</v>
+        <v>76.5</v>
       </c>
       <c r="G5">
-        <f>0.9*market_prices!J5</f>
-        <v>22.95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+        <v>79.2</v>
+      </c>
+      <c r="H5">
+        <v>103.2</v>
+      </c>
+      <c r="I5">
+        <v>46.8</v>
+      </c>
+      <c r="J5">
+        <v>25.5</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
       <c r="B6">
-        <f>1.1*market_prices!B6</f>
-        <v>40.700000000000003</v>
+        <v>37</v>
       </c>
       <c r="C6">
-        <f>1.1*market_prices!F6</f>
-        <v>61.050000000000004</v>
+        <v>64</v>
       </c>
       <c r="D6">
-        <f>1.1*market_prices!J6</f>
-        <v>20.350000000000001</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <f>0.9*market_prices!B6</f>
-        <v>33.300000000000004</v>
+        <v>78</v>
       </c>
       <c r="F6">
-        <f>0.9*market_prices!F6</f>
-        <v>49.95</v>
+        <v>55.5</v>
       </c>
       <c r="G6">
-        <f>0.9*market_prices!J6</f>
-        <v>16.650000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
+        <v>76.8</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>93.6</v>
+      </c>
+      <c r="J6">
+        <v>18.5</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -3690,15 +3415,318 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="7" width="11.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44671</v>
+      </c>
+      <c r="B2">
+        <f>1.1*market_prices!B2</f>
+        <v>52.800000000000004</v>
+      </c>
+      <c r="C2">
+        <f>1.1*market_prices!F2</f>
+        <v>52.800000000000004</v>
+      </c>
+      <c r="D2">
+        <f>1.1*market_prices!J2</f>
+        <v>52.800000000000004</v>
+      </c>
+      <c r="E2">
+        <f>0.9*market_prices!B2</f>
+        <v>43.2</v>
+      </c>
+      <c r="F2">
+        <f>0.9*market_prices!F2</f>
+        <v>43.2</v>
+      </c>
+      <c r="G2">
+        <f>0.9*market_prices!J2</f>
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44671.041666666664</v>
+      </c>
+      <c r="B3">
+        <f>1.1*market_prices!B3</f>
+        <v>66</v>
+      </c>
+      <c r="C3">
+        <f>1.1*market_prices!F3</f>
+        <v>66</v>
+      </c>
+      <c r="D3">
+        <f>1.1*market_prices!J3</f>
+        <v>66</v>
+      </c>
+      <c r="E3">
+        <f>0.9*market_prices!B3</f>
+        <v>54</v>
+      </c>
+      <c r="F3">
+        <f>0.9*market_prices!F3</f>
+        <v>54</v>
+      </c>
+      <c r="G3">
+        <f>0.9*market_prices!J3</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44671.08333321759</v>
+      </c>
+      <c r="B4">
+        <f>1.1*market_prices!B4</f>
+        <v>63.800000000000004</v>
+      </c>
+      <c r="C4">
+        <f>1.1*market_prices!F4</f>
+        <v>63.800000000000004</v>
+      </c>
+      <c r="D4">
+        <f>1.1*market_prices!J4</f>
+        <v>63.800000000000004</v>
+      </c>
+      <c r="E4">
+        <f>0.9*market_prices!B4</f>
+        <v>52.2</v>
+      </c>
+      <c r="F4">
+        <f>0.9*market_prices!F4</f>
+        <v>52.2</v>
+      </c>
+      <c r="G4">
+        <f>0.9*market_prices!J4</f>
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44671.124999826388</v>
+      </c>
+      <c r="B5">
+        <f>1.1*market_prices!B5</f>
+        <v>56.1</v>
+      </c>
+      <c r="C5">
+        <f>1.1*market_prices!F5</f>
+        <v>84.15</v>
+      </c>
+      <c r="D5">
+        <f>1.1*market_prices!J5</f>
+        <v>28.05</v>
+      </c>
+      <c r="E5">
+        <f>0.9*market_prices!B5</f>
+        <v>45.9</v>
+      </c>
+      <c r="F5">
+        <f>0.9*market_prices!F5</f>
+        <v>68.850000000000009</v>
+      </c>
+      <c r="G5">
+        <f>0.9*market_prices!J5</f>
+        <v>22.95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44671.166666435187</v>
+      </c>
+      <c r="B6">
+        <f>1.1*market_prices!B6</f>
+        <v>40.700000000000003</v>
+      </c>
+      <c r="C6">
+        <f>1.1*market_prices!F6</f>
+        <v>61.050000000000004</v>
+      </c>
+      <c r="D6">
+        <f>1.1*market_prices!J6</f>
+        <v>20.350000000000001</v>
+      </c>
+      <c r="E6">
+        <f>0.9*market_prices!B6</f>
+        <v>33.300000000000004</v>
+      </c>
+      <c r="F6">
+        <f>0.9*market_prices!F6</f>
+        <v>49.95</v>
+      </c>
+      <c r="G6">
+        <f>0.9*market_prices!J6</f>
+        <v>16.650000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC5B427A-5538-47DE-980F-BB3AB58D71B6}">
   <dimension ref="A1:BA25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B1" t="s">
@@ -3772,8 +3800,8 @@
       <c r="AZ1"/>
       <c r="BA1"/>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -3805,8 +3833,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -3838,8 +3866,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -3871,8 +3899,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -3904,8 +3932,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -3937,155 +3965,118 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -4094,39 +4085,34 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="B2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="B3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4">
         <v>0.2</v>
       </c>
     </row>
@@ -4136,167 +4122,40 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44671</v>
-      </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44671.041666666664</v>
-      </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44671.08333321759</v>
-      </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44671.124999826388</v>
-      </c>
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44671.166666435187</v>
-      </c>
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v/>
-      </c>
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v/>
-      </c>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -4305,29 +4164,191 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44671.041666666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44671.08333321759</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44671.124999826388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44671.166666435187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD670E02-665B-45B8-BC4E-9596D2C1BC55}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -4341,8 +4362,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -4356,8 +4377,8 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -4371,8 +4392,8 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -4386,8 +4407,8 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -4401,116 +4422,116 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -4521,17 +4542,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704FC51-737E-45F9-9A9E-85A96AFE5439}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -4545,7 +4566,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -4559,10 +4580,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4570,19 +4591,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE12AB76-2BDA-4ACA-A128-8CFB9FB6C8F8}">
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
-    <col min="2" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
+    <col min="2" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B1" t="s">
@@ -4613,8 +4634,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -4646,8 +4667,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -4679,8 +4700,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -4712,8 +4733,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -4745,8 +4766,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -4778,116 +4799,116 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -4897,16 +4918,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B1" t="s">
@@ -4919,8 +4940,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -4934,8 +4955,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -4949,8 +4970,8 @@
         <v>4.2857142857142856</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -4964,8 +4985,8 @@
         <v>4.2857142857142856</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -4979,8 +5000,8 @@
         <v>4.4117647058823533</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -4994,116 +5015,116 @@
         <v>4.5454545454545459</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -5116,335 +5137,335 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A1B16B-CDA9-46BD-BA51-731AA9327652}">
   <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="6">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0</v>
-      </c>
-      <c r="K2" s="6">
-        <v>0</v>
-      </c>
-      <c r="L2" s="6">
-        <v>0</v>
-      </c>
-      <c r="M2" s="6">
-        <v>0</v>
-      </c>
-      <c r="N2" s="6">
-        <v>0</v>
-      </c>
-      <c r="O2" s="6">
-        <v>1</v>
-      </c>
-      <c r="P2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3">
+        <v>1</v>
+      </c>
+      <c r="P2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6">
-        <v>0</v>
-      </c>
-      <c r="K3" s="6">
-        <v>0</v>
-      </c>
-      <c r="L3" s="6">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6">
-        <v>0</v>
-      </c>
-      <c r="N3" s="6">
-        <v>0</v>
-      </c>
-      <c r="O3" s="6">
-        <v>1</v>
-      </c>
-      <c r="P3" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B3" s="3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <v>1</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
         <v>3</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>3</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
       <c r="L4">
         <v>1E-3</v>
       </c>
-      <c r="M4" s="6">
-        <v>0</v>
-      </c>
-      <c r="N4" s="6">
-        <v>0</v>
-      </c>
-      <c r="O4" s="6">
-        <v>1</v>
-      </c>
-      <c r="P4" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
+        <v>1</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6">
-        <v>0</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
         <v>4</v>
       </c>
-      <c r="H5" s="6">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
-        <v>1</v>
-      </c>
-      <c r="J5" s="6">
-        <v>1</v>
-      </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6">
-        <v>0</v>
-      </c>
-      <c r="N5" s="6">
-        <v>0</v>
-      </c>
-      <c r="O5" s="6">
-        <v>1</v>
-      </c>
-      <c r="P5" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
+        <v>1</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>1</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
-      <c r="N6" s="6">
-        <v>0</v>
-      </c>
-      <c r="O6" s="6">
-        <v>1</v>
-      </c>
-      <c r="P6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="M8" s="6"/>
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>1</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5454,409 +5475,409 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB20090B-02A9-43B7-8D03-9C18D42920EB}">
   <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="6">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
-        <v>1</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
         <v>0.9</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="3">
         <v>0.3</v>
       </c>
-      <c r="I2" s="6">
-        <v>1</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0</v>
-      </c>
-      <c r="K2" s="6">
+      <c r="I2" s="3">
+        <v>1</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
         <v>4</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="3">
         <v>3</v>
       </c>
-      <c r="M2" s="6">
-        <v>0</v>
-      </c>
-      <c r="N2" s="6">
-        <v>0</v>
-      </c>
-      <c r="O2" s="6">
-        <v>1</v>
-      </c>
-      <c r="P2" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3">
+        <v>1</v>
+      </c>
+      <c r="P2" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="6">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="B3" s="3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
         <v>3</v>
       </c>
-      <c r="H3" s="6">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
-        <v>1</v>
-      </c>
-      <c r="J3" s="6">
-        <v>0</v>
-      </c>
-      <c r="K3" s="6">
-        <v>0</v>
-      </c>
-      <c r="L3" s="6">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6">
-        <v>0</v>
-      </c>
-      <c r="N3" s="6">
-        <v>0</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
-      </c>
-      <c r="P3" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
         <v>0.7</v>
       </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
-        <v>1</v>
-      </c>
-      <c r="J4" s="6">
-        <v>0</v>
-      </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6">
-        <v>0</v>
-      </c>
-      <c r="M4" s="6">
-        <v>0</v>
-      </c>
-      <c r="N4" s="6">
-        <v>0</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="6">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
-        <v>1</v>
-      </c>
-      <c r="J5" s="6">
-        <v>0</v>
-      </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6">
-        <v>0</v>
-      </c>
-      <c r="N5" s="6">
-        <v>0</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>1</v>
-      </c>
-      <c r="G6" s="6">
-        <v>1</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <v>1</v>
-      </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
-      <c r="N6" s="6">
-        <v>0</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
         <v>2</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="3">
         <v>0.99</v>
       </c>
-      <c r="H7" s="6">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>1</v>
-      </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5866,20 +5887,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6007B83A-95ED-43FB-AC05-C8A15D3323E5}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -5890,7 +5911,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -5901,7 +5922,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -5912,7 +5933,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -5931,48 +5952,48 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB1106B-D567-41FC-8E91-2B4CC5EC9B59}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="3">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3">
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
         <f>B1+1</f>
         <v>2</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="2">
         <f t="shared" ref="D1:K1" si="0">C1+1</f>
         <v>3</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -5985,400 +6006,399 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A86A8A7-FD76-4891-A53C-CBB095359118}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5">
-        <v>1</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>20</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2">
         <v>3</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2">
         <v>0.5</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2">
         <v>0.5</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2">
         <v>0.6</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2">
         <v>0.6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>10</v>
       </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>0.5</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3">
         <v>0.5</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3">
         <v>0.6</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3">
         <v>0.6</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>8</v>
       </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>0.5</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4">
         <v>0.5</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4">
         <v>0.6</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4">
         <v>0.6</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5">
         <v>15</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5">
         <v>0.5</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5">
         <v>0.5</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5">
         <v>0.6</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5">
         <v>0.6</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="5">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>15</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6">
         <v>0.5</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6">
         <v>0.5</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6">
         <v>0.5</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6">
         <v>0.6</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6">
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="5">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>10</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7">
         <v>15</v>
       </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>0.6</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7">
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="5">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <v>7</v>
       </c>
-      <c r="F8" s="5">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5">
-        <v>1</v>
-      </c>
-      <c r="I8" s="5">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <v>0.6</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8">
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <v>5</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9">
         <v>0.5</v>
       </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5">
-        <v>1</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
         <v>0.6</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9">
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="5">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>5</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10">
         <v>0.5</v>
       </c>
-      <c r="G10" s="5">
-        <v>1</v>
-      </c>
-      <c r="H10" s="5">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
         <v>0.6</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10">
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="5">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
         <v>20</v>
       </c>
-      <c r="F11" s="5">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5">
-        <v>1</v>
-      </c>
-      <c r="I11" s="5">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
         <v>0.6</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11">
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="5">
-        <v>1</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
         <v>20</v>
       </c>
-      <c r="F12" s="5">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5">
-        <v>1</v>
-      </c>
-      <c r="I12" s="5">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
         <v>0.6</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12">
         <v>0.6</v>
       </c>
     </row>
@@ -6391,156 +6411,156 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AEF404-3743-47D7-AC45-7AE3A9FB796E}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="str">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="str">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="str">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="str">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="str">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -6553,27 +6573,27 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A97A19-79B8-46BB-9B8D-DDA080BD4E36}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>135</v>
       </c>
     </row>

--- a/input_data/input_data_common_start.xlsx
+++ b/input_data/input_data_common_start.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA49811-00BD-47D8-9361-E7F090AA446C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A16497A-FE5E-47D9-902E-30AE92BF9BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="4" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="169">
   <si>
     <t>node</t>
   </si>
@@ -565,6 +565,9 @@
   </si>
   <si>
     <t>inflow</t>
+  </si>
+  <si>
+    <t>deviation_penalty</t>
   </si>
 </sst>
 </file>
@@ -2010,13 +2013,13 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17ADD341-DF79-42C4-A9D4-008C7FE8FB1E}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>163</v>
       </c>
@@ -2034,6 +2037,9 @@
       </c>
       <c r="F1" t="s">
         <v>167</v>
+      </c>
+      <c r="G1" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
